--- a/tools/xlsform_samples/DOSPERT.xlsx
+++ b/tools/xlsform_samples/DOSPERT.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>For each situation below, you will answer two or three questions. First, indicate how likely you are to engage in the activity. Then, indicate how risky you perceive the situation to be. Riskiness is a very personal and intuitive notion — we are interested in your gut level assessment.</t>
+          <t>For each situation below, you will answer two or three questions. First, indicate how likely you are to engage in the activity. Then, indicate how risky you perceive the situation to be. Riskiness is a very personal and intuitive notion -- we are interested in your gut level assessment.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/tools/xlsform_samples/DOSPERT.xlsx
+++ b/tools/xlsform_samples/DOSPERT.xlsx
@@ -442,14 +442,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="66" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -529,10 +529,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sec_intro</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>inst1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>For each situation below, you will answer two or three questions. First, indicate how likely you are to engage in the activity. Then, indicate how risky you perceive the situation to be. Riskiness is a very personal and intuitive notion -- we are interested in your gut level assessment.</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -546,24 +550,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>inst1</t>
+          <t>rt1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>For each situation below, you will answer two or three questions. First, indicate how likely you are to engage in the activity. Then, indicate how risky you perceive the situation to be. Riskiness is a very personal and intuitive notion -- we are interested in your gut level assessment.</t>
+          <t>Admitting that your tastes are different from those of a friend.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -572,20 +584,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sec1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>rp1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Admitting that your tastes are different from those of a friend.</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -594,12 +618,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rt1</t>
+          <t>eb1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -608,7 +632,11 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -628,17 +656,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rp1</t>
+          <t>rt2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Admitting that your tastes are different from those of a friend.</t>
+          <t>Going camping in the wilderness.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -662,25 +690,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eb1</t>
+          <t>rp2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Admitting that your tastes are different from those of a friend.</t>
+          <t>Going camping in the wilderness.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -700,20 +724,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sec2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>eb2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Going camping in the wilderness.</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -727,12 +767,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rt2</t>
+          <t>rt3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Going camping in the wilderness.</t>
+          <t>Betting a day's income at the horse races.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -761,12 +801,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rp2</t>
+          <t>rp3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Going camping in the wilderness.</t>
+          <t>Betting a day's income at the horse races.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -795,18 +835,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eb2</t>
+          <t>eb3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Going camping in the wilderness.</t>
+          <t>Betting a day's income at the horse races.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>${show_expected_benefits} = 'True'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -828,20 +868,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sec3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>rt4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investing 10% of your annual income in a moderate growth mutual fund.</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -850,17 +902,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rt3</t>
+          <t>rp4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Betting a day's income at the horse races.</t>
+          <t>Investing 10% of your annual income in a moderate growth mutual fund.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -884,21 +936,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rp3</t>
+          <t>eb4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Betting a day's income at the horse races.</t>
+          <t>Investing 10% of your annual income in a moderate growth mutual fund.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -918,25 +974,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eb3</t>
+          <t>rt5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Betting a day's income at the horse races.</t>
+          <t>Drinking heavily at a social function.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -956,20 +1008,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sec4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>rp5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Drinking heavily at a social function.</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -978,21 +1042,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rt4</t>
+          <t>eb5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Investing 10% of your annual income in a moderate growth mutual fund.</t>
+          <t>Drinking heavily at a social function.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1012,17 +1080,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rp4</t>
+          <t>rt6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Investing 10% of your annual income in a moderate growth mutual fund.</t>
+          <t>Taking some questionable deductions on your income tax return.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1046,25 +1114,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eb4</t>
+          <t>rp6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Investing 10% of your annual income in a moderate growth mutual fund.</t>
+          <t>Taking some questionable deductions on your income tax return.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1084,20 +1148,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sec5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>eb6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Taking some questionable deductions on your income tax return.</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1111,12 +1191,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rt5</t>
+          <t>rt7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Drinking heavily at a social function.</t>
+          <t>Disagreeing with an authority figure on a major issue.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1145,12 +1225,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rp5</t>
+          <t>rp7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Drinking heavily at a social function.</t>
+          <t>Disagreeing with an authority figure on a major issue.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1179,18 +1259,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eb5</t>
+          <t>eb7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Drinking heavily at a social function.</t>
+          <t>Disagreeing with an authority figure on a major issue.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>${show_expected_benefits} = 'True'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1212,20 +1292,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sec6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>rt8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Betting a day's income at a high-stake poker game.</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1234,17 +1326,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>rt6</t>
+          <t>rp8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Taking some questionable deductions on your income tax return.</t>
+          <t>Betting a day's income at a high-stake poker game.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1268,21 +1360,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rp6</t>
+          <t>eb8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Taking some questionable deductions on your income tax return.</t>
+          <t>Betting a day's income at a high-stake poker game.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1302,25 +1398,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eb6</t>
+          <t>rt9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Taking some questionable deductions on your income tax return.</t>
+          <t>Having an affair with a married man/woman.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1340,20 +1432,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sec7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>rp9</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Having an affair with a married man/woman.</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1362,21 +1466,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rt7</t>
+          <t>eb9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Disagreeing with an authority figure on a major issue.</t>
+          <t>Having an affair with a married man/woman.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1396,17 +1504,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>rp7</t>
+          <t>rt10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Disagreeing with an authority figure on a major issue.</t>
+          <t>Passing off somebody else's work as your own.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1430,25 +1538,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eb7</t>
+          <t>rp10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Disagreeing with an authority figure on a major issue.</t>
+          <t>Passing off somebody else's work as your own.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1468,20 +1572,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sec8</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>eb10</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Passing off somebody else's work as your own.</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1495,12 +1615,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rt8</t>
+          <t>rt11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Betting a day's income at a high-stake poker game.</t>
+          <t>Going down a ski run that is beyond your ability.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1529,12 +1649,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>rp8</t>
+          <t>rp11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Betting a day's income at a high-stake poker game.</t>
+          <t>Going down a ski run that is beyond your ability.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1563,18 +1683,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eb8</t>
+          <t>eb11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Betting a day's income at a high-stake poker game.</t>
+          <t>Going down a ski run that is beyond your ability.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>${show_expected_benefits} = 'True'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1596,20 +1716,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sec9</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>rt12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Investing 5% of your annual income in a very speculative stock.</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1618,17 +1750,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>rt9</t>
+          <t>rp12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Having an affair with a married man/woman.</t>
+          <t>Investing 5% of your annual income in a very speculative stock.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1652,21 +1784,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rp9</t>
+          <t>eb12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Having an affair with a married man/woman.</t>
+          <t>Investing 5% of your annual income in a very speculative stock.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1686,25 +1822,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eb9</t>
+          <t>rt13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Having an affair with a married man/woman.</t>
+          <t>Going whitewater rafting at high water in the spring.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1724,20 +1856,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sec10</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>rp13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Going whitewater rafting at high water in the spring.</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -1746,21 +1890,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>rt10</t>
+          <t>eb13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Passing off somebody else's work as your own.</t>
+          <t>Going whitewater rafting at high water in the spring.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1780,17 +1928,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>rp10</t>
+          <t>rt14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Passing off somebody else's work as your own.</t>
+          <t>Betting a day's income on the outcome of a sporting event.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1814,25 +1962,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eb10</t>
+          <t>rp14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Passing off somebody else's work as your own.</t>
+          <t>Betting a day's income on the outcome of a sporting event.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1852,20 +1996,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sec11</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>eb14</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Betting a day's income on the outcome of a sporting event.</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -1879,12 +2039,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>rt11</t>
+          <t>rt15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Going down a ski run that is beyond your ability.</t>
+          <t>Engaging in unprotected sex.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1913,12 +2073,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>rp11</t>
+          <t>rp15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Going down a ski run that is beyond your ability.</t>
+          <t>Engaging in unprotected sex.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1947,18 +2107,18 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eb11</t>
+          <t>eb15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Going down a ski run that is beyond your ability.</t>
+          <t>Engaging in unprotected sex.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>${show_expected_benefits} = 'True'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1980,20 +2140,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sec12</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>rt16</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Revealing a friend's secret to someone else.</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2002,17 +2174,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>rt12</t>
+          <t>rp16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Investing 5% of your annual income in a very speculative stock.</t>
+          <t>Revealing a friend's secret to someone else.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2036,21 +2208,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>rp12</t>
+          <t>eb16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Investing 5% of your annual income in a very speculative stock.</t>
+          <t>Revealing a friend's secret to someone else.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2070,25 +2246,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>eb12</t>
+          <t>rt17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Investing 5% of your annual income in a very speculative stock.</t>
+          <t>Driving a car without wearing a seat belt.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2108,20 +2280,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>sec13</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>rp17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Driving a car without wearing a seat belt.</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -2130,21 +2314,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>rt13</t>
+          <t>eb17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Going whitewater rafting at high water in the spring.</t>
+          <t>Driving a car without wearing a seat belt.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2164,17 +2352,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>rp13</t>
+          <t>rt18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Going whitewater rafting at high water in the spring.</t>
+          <t>Investing 10% of your annual income in a new business venture.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2198,25 +2386,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eb13</t>
+          <t>rp18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Going whitewater rafting at high water in the spring.</t>
+          <t>Investing 10% of your annual income in a new business venture.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2236,20 +2420,36 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>sec14</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>eb18</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Investing 10% of your annual income in a new business venture.</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -2263,12 +2463,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>rt14</t>
+          <t>rt19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Betting a day's income on the outcome of a sporting event.</t>
+          <t>Taking a skydiving class.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2297,12 +2497,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>rp14</t>
+          <t>rp19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Betting a day's income on the outcome of a sporting event.</t>
+          <t>Taking a skydiving class.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2331,18 +2531,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eb14</t>
+          <t>eb19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Betting a day's income on the outcome of a sporting event.</t>
+          <t>Taking a skydiving class.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>${show_expected_benefits} = 'True'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2364,20 +2564,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sec15</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>rt20</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Riding a motorcycle without a helmet.</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -2386,17 +2598,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rt15</t>
+          <t>rp20</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Engaging in unprotected sex.</t>
+          <t>Riding a motorcycle without a helmet.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2420,21 +2632,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>rp15</t>
+          <t>eb20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Engaging in unprotected sex.</t>
+          <t>Riding a motorcycle without a helmet.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2454,25 +2670,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eb15</t>
+          <t>rt21</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Engaging in unprotected sex.</t>
+          <t>Choosing a career that you truly enjoy over a more secure one.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2492,20 +2704,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>sec16</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>rp21</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Choosing a career that you truly enjoy over a more secure one.</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -2514,21 +2738,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>rt16</t>
+          <t>eb21</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Revealing a friend's secret to someone else.</t>
+          <t>Choosing a career that you truly enjoy over a more secure one.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2548,17 +2776,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>rp16</t>
+          <t>rt22</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Revealing a friend's secret to someone else.</t>
+          <t>Speaking your mind about an unpopular issue in a meeting at work.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2582,25 +2810,21 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eb16</t>
+          <t>rp22</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Revealing a friend's secret to someone else.</t>
+          <t>Speaking your mind about an unpopular issue in a meeting at work.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2620,20 +2844,36 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>sec17</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>eb22</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Speaking your mind about an unpopular issue in a meeting at work.</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -2647,12 +2887,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>rt17</t>
+          <t>rt23</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Driving a car without wearing a seat belt.</t>
+          <t>Sunbathing without sunscreen.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2681,12 +2921,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>rp17</t>
+          <t>rp23</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Driving a car without wearing a seat belt.</t>
+          <t>Sunbathing without sunscreen.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2715,18 +2955,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>eb17</t>
+          <t>eb23</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Driving a car without wearing a seat belt.</t>
+          <t>Sunbathing without sunscreen.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>${show_expected_benefits} = 'True'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2748,20 +2988,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>sec18</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>rt24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bungee jumping off a tall bridge.</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -2770,17 +3022,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>rt18</t>
+          <t>rp24</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Investing 10% of your annual income in a new business venture.</t>
+          <t>Bungee jumping off a tall bridge.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2804,21 +3056,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>rp18</t>
+          <t>eb24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Investing 10% of your annual income in a new business venture.</t>
+          <t>Bungee jumping off a tall bridge.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2838,25 +3094,21 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>eb18</t>
+          <t>rt25</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Investing 10% of your annual income in a new business venture.</t>
+          <t>Piloting a small plane.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2876,20 +3128,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>sec19</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>rp25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Piloting a small plane.</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -2898,21 +3162,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>rt19</t>
+          <t>eb25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Taking a skydiving class.</t>
+          <t>Piloting a small plane.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2932,17 +3200,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>rp19</t>
+          <t>rt26</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Taking a skydiving class.</t>
+          <t>Walking home alone at night in an unsafe area of town.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2966,25 +3234,21 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>eb19</t>
+          <t>rp26</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Taking a skydiving class.</t>
+          <t>Walking home alone at night in an unsafe area of town.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3004,20 +3268,36 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>sec20</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>eb26</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Walking home alone at night in an unsafe area of town.</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3031,12 +3311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>rt20</t>
+          <t>rt27</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Riding a motorcycle without a helmet.</t>
+          <t>Moving to a city far away from your extended family.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3065,12 +3345,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>rp20</t>
+          <t>rp27</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Riding a motorcycle without a helmet.</t>
+          <t>Moving to a city far away from your extended family.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3099,18 +3379,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>eb20</t>
+          <t>eb27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Riding a motorcycle without a helmet.</t>
+          <t>Moving to a city far away from your extended family.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>${show_expected_benefits} = 'True'</t>
+          <t>true()</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3132,20 +3412,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>sec21</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>rt28</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Starting a new career in your mid-thirties.</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -3154,17 +3446,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>rt21</t>
+          <t>rp28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Choosing a career that you truly enjoy over a more secure one.</t>
+          <t>Starting a new career in your mid-thirties.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3188,21 +3480,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>rp21</t>
+          <t>eb28</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Choosing a career that you truly enjoy over a more secure one.</t>
+          <t>Starting a new career in your mid-thirties.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3222,25 +3518,21 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>eb21</t>
+          <t>rt29</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Choosing a career that you truly enjoy over a more secure one.</t>
+          <t>Leaving your young children alone at home while running an errand.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3260,20 +3552,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>sec22</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>rp29</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Leaving your young children alone at home while running an errand.</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -3282,21 +3586,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>rt22</t>
+          <t>eb29</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Speaking your mind about an unpopular issue in a meeting at work.</t>
+          <t>Leaving your young children alone at home while running an errand.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3316,17 +3624,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>select_one likert_main</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>rp22</t>
+          <t>rt30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Speaking your mind about an unpopular issue in a meeting at work.</t>
+          <t>Not returning a wallet you found that contains $200.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -3350,25 +3658,21 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>select_one rp_opts</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>eb22</t>
+          <t>rp30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Speaking your mind about an unpopular issue in a meeting at work.</t>
+          <t>Not returning a wallet you found that contains $200.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3388,20 +3692,36 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one eb_opts</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>sec23</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>eb30</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Not returning a wallet you found that contains $200.</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>likert</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -3410,32 +3730,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>rt23</t>
+          <t>DOSPERT_rt_ethical</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sunbathing without sunscreen.</t>
+          <t>rt_ethical (mean_coded) - Mean of 6 ethical risk-taking items (1-7).</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>(${rt6} + ${rt9} + ${rt10} + ${rt16} + ${rt29} + ${rt30}) div 6</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -3444,32 +3760,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>rp23</t>
+          <t>DOSPERT_rt_financial</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sunbathing without sunscreen.</t>
+          <t>rt_financial (mean_coded) - Mean of 6 financial risk-taking items (1-7).</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>(${rt3} + ${rt4} + ${rt8} + ${rt12} + ${rt14} + ${rt18}) div 6</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -3478,36 +3790,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>eb23</t>
+          <t>DOSPERT_rt_health_safety</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sunbathing without sunscreen.</t>
+          <t>rt_health_safety (mean_coded) - Mean of 6 health/safety risk-taking items (1-7).</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>(${rt5} + ${rt15} + ${rt17} + ${rt20} + ${rt23} + ${rt26}) div 6</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -3516,19 +3820,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>sec24</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>DOSPERT_rt_recreational</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>rt_recreational (mean_coded) - Mean of 6 recreational risk-taking items (1-7).</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>(${rt2} + ${rt11} + ${rt13} + ${rt19} + ${rt24} + ${rt25}) div 6</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
@@ -3538,32 +3850,28 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>rt24</t>
+          <t>DOSPERT_rt_social</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bungee jumping off a tall bridge.</t>
+          <t>rt_social (mean_coded) - Mean of 6 social risk-taking items (1-7).</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>(${rt1} + ${rt7} + ${rt21} + ${rt22} + ${rt27} + ${rt28}) div 6</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -3572,32 +3880,28 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>rp24</t>
+          <t>DOSPERT_rp_ethical</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bungee jumping off a tall bridge.</t>
+          <t>rp_ethical (mean_coded) - Mean of 6 ethical risk perception items (1-7).</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>(${rp6} + ${rp9} + ${rp10} + ${rp16} + ${rp29} + ${rp30}) div 6</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -3606,36 +3910,28 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>eb24</t>
+          <t>DOSPERT_rp_financial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bungee jumping off a tall bridge.</t>
+          <t>rp_financial (mean_coded) - Mean of 6 financial risk perception items (1-7).</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>(${rp3} + ${rp4} + ${rp8} + ${rp12} + ${rp14} + ${rp18}) div 6</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -3644,19 +3940,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>sec25</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
+          <t>DOSPERT_rp_health_safety</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>rp_health_safety (mean_coded) - Mean of 6 health/safety risk perception items (1-7).</t>
+        </is>
+      </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>(${rp5} + ${rp15} + ${rp17} + ${rp20} + ${rp23} + ${rp26}) div 6</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
@@ -3666,32 +3970,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>rt25</t>
+          <t>DOSPERT_rp_recreational</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Piloting a small plane.</t>
+          <t>rp_recreational (mean_coded) - Mean of 6 recreational risk perception items (1-7).</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>(${rp2} + ${rp11} + ${rp13} + ${rp19} + ${rp24} + ${rp25}) div 6</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -3700,32 +4000,28 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>rp25</t>
+          <t>DOSPERT_rp_social</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Piloting a small plane.</t>
+          <t>rp_social (mean_coded) - Mean of 6 social risk perception items (1-7).</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>(${rp1} + ${rp7} + ${rp21} + ${rp22} + ${rp27} + ${rp28}) div 6</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -3734,36 +4030,28 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>eb25</t>
+          <t>DOSPERT_eb_ethical</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Piloting a small plane.</t>
+          <t>eb_ethical (mean_coded) - Mean of 6 ethical expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>(${eb6} + ${eb9} + ${eb10} + ${eb16} + ${eb29} + ${eb30}) div 6</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -3772,19 +4060,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>sec26</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>DOSPERT_eb_financial</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>eb_financial (mean_coded) - Mean of 6 financial expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>(${eb3} + ${eb4} + ${eb8} + ${eb12} + ${eb14} + ${eb18}) div 6</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -3794,32 +4090,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>select_one likert_main</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>rt26</t>
+          <t>DOSPERT_eb_health_safety</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Walking home alone at night in an unsafe area of town.</t>
+          <t>eb_health_safety (mean_coded) - Mean of 6 health/safety expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>(${eb5} + ${eb15} + ${eb17} + ${eb20} + ${eb23} + ${eb26}) div 6</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -3828,32 +4120,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>select_one rp_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>rp26</t>
+          <t>DOSPERT_eb_recreational</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Walking home alone at night in an unsafe area of town.</t>
+          <t>eb_recreational (mean_coded) - Mean of 6 recreational expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>(${eb2} + ${eb11} + ${eb13} + ${eb19} + ${eb24} + ${eb25}) div 6</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -3862,1054 +4150,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>select_one eb_opts</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>eb26</t>
+          <t>DOSPERT_eb_social</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Walking home alone at night in an unsafe area of town.</t>
+          <t>eb_social (mean_coded) - Mean of 6 social expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>(${eb1} + ${eb7} + ${eb21} + ${eb22} + ${eb27} + ${eb28}) div 6</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>sec27</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>select_one likert_main</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>rt27</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Moving to a city far away from your extended family.</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>select_one rp_opts</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>rp27</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Moving to a city far away from your extended family.</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>select_one eb_opts</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>eb27</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Moving to a city far away from your extended family.</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>sec28</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>select_one likert_main</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>rt28</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Starting a new career in your mid-thirties.</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>select_one rp_opts</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>rp28</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Starting a new career in your mid-thirties.</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>select_one eb_opts</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>eb28</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Starting a new career in your mid-thirties.</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>sec29</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>select_one likert_main</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>rt29</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Leaving your young children alone at home while running an errand.</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>select_one rp_opts</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>rp29</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Leaving your young children alone at home while running an errand.</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>select_one eb_opts</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>eb29</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Leaving your young children alone at home while running an errand.</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>sec30</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>select_one likert_main</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>rt30</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Not returning a wallet you found that contains $200.</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>select_one rp_opts</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>rp30</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Not returning a wallet you found that contains $200.</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>select_one eb_opts</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>eb30</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Not returning a wallet you found that contains $200.</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>${show_expected_benefits} = 'True'</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>likert</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>DOSPERT_scoring</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Computed Scores</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>DOSPERT_rt_ethical</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>rt_ethical (mean_coded) - Mean of 6 ethical risk-taking items (1-7).</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>(${rt6} + ${rt9} + ${rt10} + ${rt16} + ${rt29} + ${rt30}) div 6</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>DOSPERT_rt_financial</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>rt_financial (mean_coded) - Mean of 6 financial risk-taking items (1-7).</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>(${rt3} + ${rt4} + ${rt8} + ${rt12} + ${rt14} + ${rt18}) div 6</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>DOSPERT_rt_health_safety</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>rt_health_safety (mean_coded) - Mean of 6 health/safety risk-taking items (1-7).</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>(${rt5} + ${rt15} + ${rt17} + ${rt20} + ${rt23} + ${rt26}) div 6</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>DOSPERT_rt_recreational</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>rt_recreational (mean_coded) - Mean of 6 recreational risk-taking items (1-7).</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>(${rt2} + ${rt11} + ${rt13} + ${rt19} + ${rt24} + ${rt25}) div 6</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>DOSPERT_rt_social</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>rt_social (mean_coded) - Mean of 6 social risk-taking items (1-7).</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>(${rt1} + ${rt7} + ${rt21} + ${rt22} + ${rt27} + ${rt28}) div 6</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>DOSPERT_rp_ethical</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>rp_ethical (mean_coded) - Mean of 6 ethical risk perception items (1-7).</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>(${rp6} + ${rp9} + ${rp10} + ${rp16} + ${rp29} + ${rp30}) div 6</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>DOSPERT_rp_financial</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>rp_financial (mean_coded) - Mean of 6 financial risk perception items (1-7).</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>(${rp3} + ${rp4} + ${rp8} + ${rp12} + ${rp14} + ${rp18}) div 6</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>DOSPERT_rp_health_safety</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>rp_health_safety (mean_coded) - Mean of 6 health/safety risk perception items (1-7).</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>(${rp5} + ${rp15} + ${rp17} + ${rp20} + ${rp23} + ${rp26}) div 6</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>DOSPERT_rp_recreational</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>rp_recreational (mean_coded) - Mean of 6 recreational risk perception items (1-7).</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>(${rp2} + ${rp11} + ${rp13} + ${rp19} + ${rp24} + ${rp25}) div 6</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>DOSPERT_rp_social</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>rp_social (mean_coded) - Mean of 6 social risk perception items (1-7).</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>(${rp1} + ${rp7} + ${rp21} + ${rp22} + ${rp27} + ${rp28}) div 6</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>DOSPERT_eb_ethical</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>eb_ethical (mean_coded) - Mean of 6 ethical expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>(${eb6} + ${eb9} + ${eb10} + ${eb16} + ${eb29} + ${eb30}) div 6</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>DOSPERT_eb_financial</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>eb_financial (mean_coded) - Mean of 6 financial expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>(${eb3} + ${eb4} + ${eb8} + ${eb12} + ${eb14} + ${eb18}) div 6</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>DOSPERT_eb_health_safety</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>eb_health_safety (mean_coded) - Mean of 6 health/safety expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>(${eb5} + ${eb15} + ${eb17} + ${eb20} + ${eb23} + ${eb26}) div 6</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>DOSPERT_eb_recreational</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>eb_recreational (mean_coded) - Mean of 6 recreational expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>(${eb2} + ${eb11} + ${eb13} + ${eb19} + ${eb24} + ${eb25}) div 6</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>DOSPERT_eb_social</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>eb_social (mean_coded) - Mean of 6 social expected benefits items (1-7). Only scored when show_expected_benefits is enabled.</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>(${eb1} + ${eb7} + ${eb21} + ${eb22} + ${eb27} + ${eb28}) div 6</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>DOSPERT_scoring</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/DOSPERT.xlsx
+++ b/tools/xlsform_samples/DOSPERT.xlsx
@@ -4628,7 +4628,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
